--- a/artfynd/A 59433-2025 artfynd.xlsx
+++ b/artfynd/A 59433-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>

--- a/artfynd/A 59433-2025 artfynd.xlsx
+++ b/artfynd/A 59433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67532671</v>
+        <v>118557088</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Marsliden, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519259.075516169</v>
+        <v>519293</v>
       </c>
       <c r="R2" t="n">
-        <v>7209356.769517107</v>
+        <v>7209349</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eino Kenttä</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67532693</v>
+        <v>118557141</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Marsliden, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519059.3061103688</v>
+        <v>519152</v>
       </c>
       <c r="R3" t="n">
-        <v>7209270.884435331</v>
+        <v>7209713</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eino Kenttä</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67532727</v>
+        <v>118557041</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Marsliden, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519258.6520269547</v>
+        <v>519117</v>
       </c>
       <c r="R4" t="n">
-        <v>7209356.766780315</v>
+        <v>7209453</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eino Kenttä</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67532761</v>
+        <v>118557043</v>
       </c>
       <c r="B5" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Marsliden, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519142.3038764276</v>
+        <v>519151</v>
       </c>
       <c r="R5" t="n">
-        <v>7209338.674198138</v>
+        <v>7209748</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eino Kenttä</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85411462</v>
+        <v>118557127</v>
       </c>
       <c r="B6" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,40 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ströcka, Marsliden, Ås lm</t>
+          <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519156.2056931636</v>
+        <v>519148</v>
       </c>
       <c r="R6" t="n">
-        <v>7209350.184514301</v>
+        <v>7209739</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,72 +1128,42 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal angripen fruktkropp på granhögstubbe. Mycket sporer hittades ändå.</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Tobias Pettersson, Eino Kenttä</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103797753</v>
+        <v>103797752</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519065.273013729</v>
+        <v>519099</v>
       </c>
       <c r="R7" t="n">
-        <v>7209265.000458612</v>
+        <v>7209274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,19 +1228,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103797744</v>
+        <v>67532727</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Kallkällmyran, Marsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519385.1429795702</v>
+        <v>519259</v>
       </c>
       <c r="R8" t="n">
-        <v>7209443.031307993</v>
+        <v>7209357</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103797772</v>
+        <v>118557112</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519557.3787834637</v>
+        <v>519073</v>
       </c>
       <c r="R9" t="n">
-        <v>7209010.564319931</v>
+        <v>7209526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1444,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103797758</v>
+        <v>103797738</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519014.3645863436</v>
+        <v>519810</v>
       </c>
       <c r="R10" t="n">
-        <v>7208946.554339063</v>
+        <v>7208826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103797734</v>
+        <v>103797760</v>
       </c>
       <c r="B11" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4217</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519864.4718161168</v>
+        <v>519020</v>
       </c>
       <c r="R11" t="n">
-        <v>7208690.638331162</v>
+        <v>7208928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103797771</v>
+        <v>103797750</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519551.5879932571</v>
+        <v>519130</v>
       </c>
       <c r="R12" t="n">
-        <v>7208989.373871145</v>
+        <v>7209212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,19 +1713,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103797757</v>
+        <v>103797755</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1965,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518986.4751275248</v>
+        <v>518986</v>
       </c>
       <c r="R13" t="n">
-        <v>7208936.22320134</v>
+        <v>7209197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,19 +1810,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103797738</v>
+        <v>103797739</v>
       </c>
       <c r="B14" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519809.7769222219</v>
+        <v>519783</v>
       </c>
       <c r="R14" t="n">
-        <v>7208825.661210883</v>
+        <v>7208927</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,19 +1907,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103797760</v>
+        <v>103797756</v>
       </c>
       <c r="B15" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2189,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519019.5686309362</v>
+        <v>518974</v>
       </c>
       <c r="R15" t="n">
-        <v>7208927.549979056</v>
+        <v>7209194</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,19 +2004,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103797749</v>
+        <v>103797759</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2301,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519135.9356063335</v>
+        <v>519023</v>
       </c>
       <c r="R16" t="n">
-        <v>7209209.192392414</v>
+        <v>7208937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,19 +2101,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,12 +2133,7 @@
         <v>103797716</v>
       </c>
       <c r="B17" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519917.5955129223</v>
+        <v>519917</v>
       </c>
       <c r="R17" t="n">
-        <v>7208601.295616849</v>
+        <v>7208601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,19 +2198,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103797739</v>
+        <v>103797741</v>
       </c>
       <c r="B18" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519782.4156685684</v>
+        <v>519786</v>
       </c>
       <c r="R18" t="n">
-        <v>7208927.438667218</v>
+        <v>7209010</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,19 +2295,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103797752</v>
+        <v>103797774</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2637,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519099.0935521948</v>
+        <v>519677</v>
       </c>
       <c r="R19" t="n">
-        <v>7209274.523230041</v>
+        <v>7209244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,19 +2392,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103797755</v>
+        <v>67532761</v>
       </c>
       <c r="B20" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,37 +2432,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Kallkällmyran, Marsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518986.0830539116</v>
+        <v>519142</v>
       </c>
       <c r="R20" t="n">
-        <v>7209197.23547848</v>
+        <v>7209339</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2779,22 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,65 +2506,63 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103797770</v>
+        <v>85411462</v>
       </c>
       <c r="B21" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Ströcka, Marsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519550.7131617495</v>
+        <v>519156</v>
       </c>
       <c r="R21" t="n">
-        <v>7208993.598635956</v>
+        <v>7209350</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2891,57 +2586,57 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammal angripen fruktkropp på granhögstubbe. Mycket sporer hittades ändå.</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström, Tobias Pettersson, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103797754</v>
+        <v>103797733</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,21 +2644,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2973,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519028.4720462239</v>
+        <v>519902</v>
       </c>
       <c r="R22" t="n">
-        <v>7209191.583533196</v>
+        <v>7208571</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,22 +2698,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,55 +2730,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103797737</v>
+        <v>103797734</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519792.3917086375</v>
+        <v>519864</v>
       </c>
       <c r="R23" t="n">
-        <v>7208764.622396748</v>
+        <v>7208690</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,19 +2798,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,37 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103797742</v>
+        <v>103797773</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3202,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519780.1964730677</v>
+        <v>519653</v>
       </c>
       <c r="R24" t="n">
-        <v>7209006.535089437</v>
+        <v>7209161</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3232,22 +2892,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,53 +2924,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103797736</v>
+        <v>67532671</v>
       </c>
       <c r="B25" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kallkällmyran, Ås lm</t>
+          <t>Kallkällmyran, Marsliden, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519829.1469118838</v>
+        <v>519259</v>
       </c>
       <c r="R25" t="n">
-        <v>7208779.251461716</v>
+        <v>7209357</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3344,22 +2989,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,49 +3009,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Isak Vahlström, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103797735</v>
+        <v>103797742</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3426,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519846.9612127075</v>
+        <v>519780</v>
       </c>
       <c r="R26" t="n">
-        <v>7208712.099387561</v>
+        <v>7209006</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3459,19 +3089,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,37 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103797733</v>
+        <v>103797754</v>
       </c>
       <c r="B27" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3538,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519902.1229834306</v>
+        <v>519028</v>
       </c>
       <c r="R27" t="n">
-        <v>7208571.151578026</v>
+        <v>7209192</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,22 +3183,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,37 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103797750</v>
+        <v>103797777</v>
       </c>
       <c r="B28" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3650,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519129.9874577634</v>
+        <v>519570</v>
       </c>
       <c r="R28" t="n">
-        <v>7209212.115335332</v>
+        <v>7209359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,19 +3283,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,37 +3312,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103797731</v>
+        <v>118557040</v>
       </c>
       <c r="B29" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3762,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519896.4269460519</v>
+        <v>519135</v>
       </c>
       <c r="R29" t="n">
-        <v>7208535.995172121</v>
+        <v>7209398</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,22 +3377,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,44 +3402,39 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103797756</v>
+        <v>118557065</v>
       </c>
       <c r="B30" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3874,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518974.2435740439</v>
+        <v>519065</v>
       </c>
       <c r="R30" t="n">
-        <v>7209194.198936418</v>
+        <v>7209625</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,22 +3474,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3939,44 +3499,39 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103797769</v>
+        <v>118557066</v>
       </c>
       <c r="B31" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519497.5568268641</v>
+        <v>519063</v>
       </c>
       <c r="R31" t="n">
-        <v>7208766.910125876</v>
+        <v>7209739</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4016,22 +3571,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,44 +3596,39 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103797740</v>
+        <v>118557091</v>
       </c>
       <c r="B32" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519761.7683075026</v>
+        <v>519134</v>
       </c>
       <c r="R32" t="n">
-        <v>7208975.107083768</v>
+        <v>7209766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4128,22 +3668,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4163,44 +3693,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103797773</v>
+        <v>118557089</v>
       </c>
       <c r="B33" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4210,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519652.5373525057</v>
+        <v>519062</v>
       </c>
       <c r="R33" t="n">
-        <v>7209160.52236886</v>
+        <v>7209599</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,22 +3765,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,6 +3779,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4275,44 +3791,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103797774</v>
+        <v>103797770</v>
       </c>
       <c r="B34" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,10 +3833,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519677.3981784645</v>
+        <v>519551</v>
       </c>
       <c r="R34" t="n">
-        <v>7209244.021492057</v>
+        <v>7208993</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4355,19 +3866,9 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,37 +3895,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103797741</v>
+        <v>103797771</v>
       </c>
       <c r="B35" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4434,10 +3930,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519786.5242844342</v>
+        <v>519552</v>
       </c>
       <c r="R35" t="n">
-        <v>7209010.38452624</v>
+        <v>7208990</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4464,22 +3960,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,15 +3992,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103797775</v>
+        <v>103797737</v>
       </c>
       <c r="B36" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4522,34 +4003,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519567.7879626075</v>
+        <v>519793</v>
       </c>
       <c r="R36" t="n">
-        <v>7209360.472571781</v>
+        <v>7208765</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,22 +4062,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4618,15 +4094,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103797777</v>
+        <v>118557140</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4634,34 +4105,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kallkällmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519569.9192946185</v>
+        <v>519162</v>
       </c>
       <c r="R37" t="n">
-        <v>7209358.371575806</v>
+        <v>7209703</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,22 +4168,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4723,1788 +4193,10 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Elias Forsberg, Anna Johansson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>103797759</v>
-      </c>
-      <c r="B38" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>519022.4740848868</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7208936.875788655</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>103797718</v>
-      </c>
-      <c r="B39" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>519666.0446717818</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7208718.092849369</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>118557141</v>
-      </c>
-      <c r="B40" t="n">
-        <v>74597</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>308</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>519152</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7209713</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>118557066</v>
-      </c>
-      <c r="B41" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>519063</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7209739</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>118557092</v>
-      </c>
-      <c r="B42" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>519070</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7209735</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>118557089</v>
-      </c>
-      <c r="B43" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>519062</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7209599</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>118557127</v>
-      </c>
-      <c r="B44" t="n">
-        <v>77440</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>314</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Vitskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis viridialba</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>519148</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7209739</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>118557043</v>
-      </c>
-      <c r="B45" t="n">
-        <v>77440</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>314</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vitskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis viridialba</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>519151</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7209748</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>118557140</v>
-      </c>
-      <c r="B46" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>519162</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7209703</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>118557040</v>
-      </c>
-      <c r="B47" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>519135</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7209398</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>118557111</v>
-      </c>
-      <c r="B48" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>519126</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7209438</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>118557088</v>
-      </c>
-      <c r="B49" t="n">
-        <v>90460</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>112</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Stjärntagging</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Asterodon ferruginosus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>519293</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7209349</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>118557091</v>
-      </c>
-      <c r="B50" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>519134</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7209766</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>118548926</v>
-      </c>
-      <c r="B51" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Kallkällmyran (Kallkällmyran), Ås lm</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>519072</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7209670</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Anna Johansson, Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>118557112</v>
-      </c>
-      <c r="B52" t="n">
-        <v>78575</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>864</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>519073</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7209526</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>118557065</v>
-      </c>
-      <c r="B53" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>519065</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7209625</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>118557041</v>
-      </c>
-      <c r="B54" t="n">
-        <v>77440</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>314</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Vitskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis viridialba</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Kallkällmyran, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>519117</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7209453</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Elias Forsberg, Anna Johansson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
